--- a/outputs/second_outreach_non_replies.xlsx
+++ b/outputs/second_outreach_non_replies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,22 +501,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Afiq Fariz</t>
+          <t>Aizat Kun Kap</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34935708949349416</t>
+          <t>27216230574644767</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34935708949349416</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/27216230574644767</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1317485404&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=684287761&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -559,22 +559,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aizat Kun Kap</t>
+          <t>An Joe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27216230574644767</t>
+          <t>26127256943623816</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27216230574644767</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26127256943623816</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=684287761&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000583416829&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -617,22 +617,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alex Chan</t>
+          <t>Angah Angah</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25787207267568860</t>
+          <t>34712678605043381</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25787207267568860</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/34712678605043381</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100026090914958&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100055345402395&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,22 +675,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>An Joe</t>
+          <t>ARe Jim</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26127256943623816</t>
+          <t>34971028329210916</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26127256943623816</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/34971028329210916</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000583416829&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000142543063&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -733,22 +733,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Angah Angah</t>
+          <t>Arni Ani</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>34712678605043381</t>
+          <t>1357178726</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34712678605043381</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/1357178726</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100055345402395&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100067437731127&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,22 +791,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARe Jim</t>
+          <t>Azfar Azrie</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34971028329210916</t>
+          <t>26414920311434301</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34971028329210916</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26414920311434301</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000142543063&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000579700461&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -849,22 +849,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Arni Ani</t>
+          <t>Aziana Nazri</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1357178726</t>
+          <t>26592970736982414</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/1357178726</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26592970736982414</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100067437731127&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000482512311&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -907,22 +907,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Azfar Azrie</t>
+          <t>Azli Abd Rahim</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>26414920311434301</t>
+          <t>34881210441524280</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26414920311434301</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/34881210441524280</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000579700461&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1382894463&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -965,22 +965,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azi Mah</t>
+          <t>Ct Ayu</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25925220943818297</t>
+          <t>27061818516739837</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25925220943818297</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/27061818516739837</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1299042586&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000573902187&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1023,22 +1023,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Aziana Nazri</t>
+          <t>Fairous BI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26592970736982414</t>
+          <t>26978487381734820</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26592970736982414</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26978487381734820</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000482512311&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1640050421&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1081,22 +1081,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azli Abd Rahim</t>
+          <t>Fendi Zainuddin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>34881210441524280</t>
+          <t>26717952801155266</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34881210441524280</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26717952801155266</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1382894463&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100039900374594&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1139,22 +1139,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ct Ayu</t>
+          <t>Fieyza Peace</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>27061818516739837</t>
+          <t>1864364624</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27061818516739837</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/1864364624</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000573902187&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001180363328&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1197,22 +1197,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eizec Harith</t>
+          <t>Firdaus Hakimi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34683450771303418</t>
+          <t>26680069594958068</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34683450771303418</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26680069594958068</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=538643149&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100046264268160&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1255,22 +1255,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fairous BI</t>
+          <t>Hazirah Manies Haji Johari</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26978487381734820</t>
+          <t>27281904188073877</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26978487381734820</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/27281904188073877</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1640050421&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001011739892&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1313,22 +1313,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Fendi Zainuddin</t>
+          <t>Idha Idris</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26717952801155266</t>
+          <t>26896237420064278</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26717952801155266</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26896237420064278</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100039900374594&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000996677070&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1371,22 +1371,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fezy Lah Deen</t>
+          <t>Ikhwan Shafiq</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27642021585386706</t>
+          <t>26691290700480494</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27642021585386706</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26691290700480494</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001797506416&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100045013151267&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1429,22 +1429,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fieyza Peace</t>
+          <t>Jue Herman</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1864364624</t>
+          <t>856282500</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/1864364624</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/856282500</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001180363328&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000312458870&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1487,22 +1487,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Firdaus Hakimi</t>
+          <t>Kam Wai Kwan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>26680069594958068</t>
+          <t>25230176969988610</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26680069594958068</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25230176969988610</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100046264268160&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000245252190&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1545,22 +1545,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hazirah Manies Haji Johari</t>
+          <t>Khawlah Al Azwar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27281904188073877</t>
+          <t>26988101557453565</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27281904188073877</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26988101557453565</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001011739892&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100009391375701&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1603,22 +1603,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Himawar Tintin Rie</t>
+          <t>Kirtanah Ravintharan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>25901772266190399</t>
+          <t>26327752256875020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25901772266190399</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26327752256875020</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=612614381&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100012466278573&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Replied</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1661,22 +1661,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Idha Idris</t>
+          <t>Lee Pei Ting</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>26896237420064278</t>
+          <t>25465212196488673</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26896237420064278</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25465212196488673</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000996677070&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001840619253&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1719,22 +1719,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ikhwan Shafiq</t>
+          <t>Lukman Haqem</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>26691290700480494</t>
+          <t>26297421923276894</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26691290700480494</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26297421923276894</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100045013151267&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100002384231146&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1777,22 +1777,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JChiang Choon Han</t>
+          <t>Maria Muhayadin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>25745635091778097</t>
+          <t>26575694985402794</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25745635091778097</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26575694985402794</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=605325104&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=728972526&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Replied</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1835,22 +1835,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jue Herman</t>
+          <t>Muhammad Zazmie Bin Amirudin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>856282500</t>
+          <t>26763040910027742</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/856282500</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26763040910027742</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000312458870&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000584058289&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1893,22 +1893,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kam Wai Kwan</t>
+          <t>Must Leyzha</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>25230176969988610</t>
+          <t>26109445212060830</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25230176969988610</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26109445212060830</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000245252190&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000357304171&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1951,22 +1951,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Khawlah Al Azwar</t>
+          <t>Nazatul Farhanis</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>26988101557453565</t>
+          <t>26556939267307727</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26988101557453565</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26556939267307727</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100009391375701&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100005207852406&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2009,22 +2009,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kirtanah Ravintharan</t>
+          <t>Nisya MK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>26327752256875020</t>
+          <t>27418689047734291</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26327752256875020</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/27418689047734291</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100012466278573&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100016879038969&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2067,22 +2067,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lee Pei Ting</t>
+          <t>Noor Akmawati</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>25465212196488673</t>
+          <t>26750549121248717</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25465212196488673</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26750549121248717</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001840619253&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000967956207&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2125,22 +2125,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lukman Haqem</t>
+          <t>Normah Hussin Snowwhite</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>26297421923276894</t>
+          <t>27126157506973707</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26297421923276894</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/27126157506973707</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100002384231146&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100007315901018&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2183,22 +2183,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mar Zu</t>
+          <t>Nur Hidayah</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>26542654198703925</t>
+          <t>34244179895228874</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26542654198703925</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/34244179895228874</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=61567040924237&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100040767291999&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2241,22 +2241,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maria Muhayadin</t>
+          <t>Nur Kiawati Wahib</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26575694985402794</t>
+          <t>26623628940658692</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26575694985402794</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26623628940658692</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=728972526&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100003056737346&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2299,22 +2299,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Miha Mus</t>
+          <t>Nuraina Shahirah</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>26491023933852643</t>
+          <t>26102771442752311</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26491023933852643</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26102771442752311</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=578131436&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100010187793274&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2357,22 +2357,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Mohamad Azhar Aziz MaxArt</t>
+          <t>Nurarina Khidir</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1999875204</t>
+          <t>26564918653192753</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/1999875204</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26564918653192753</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100029908474750&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100002452361904&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2415,22 +2415,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mohd Khairul Hafiz</t>
+          <t>Nurnadia Kamaruzzaman</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>26655419207422712</t>
+          <t>26692733340416745</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26655419207422712</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26692733340416745</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100006833350409&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000512649285&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2473,22 +2473,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Muhammad Zazmie Bin Amirudin</t>
+          <t>Nurul Knewrul</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>26763040910027742</t>
+          <t>35133283479620209</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26763040910027742</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/35133283479620209</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000584058289&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001049088069&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2531,22 +2531,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Must Leyzha</t>
+          <t>Rasidah Rosmanan</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>26109445212060830</t>
+          <t>35023451573969923</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26109445212060830</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/35023451573969923</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000357304171&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001914029091&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2589,22 +2589,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nazatul Farhanis</t>
+          <t>Rijah Weiwei</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>26556939267307727</t>
+          <t>26456046297334143</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26556939267307727</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26456046297334143</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100005207852406&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000960038530&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2647,22 +2647,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nisya MK</t>
+          <t>Salmah Jaafar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>27418689047734291</t>
+          <t>26750312877989179</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27418689047734291</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100016879038969&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000547021795&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2705,22 +2705,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Noor Akmawati</t>
+          <t>Sariffudin Fiza</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>26750549121248717</t>
+          <t>25640455475627828</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26750549121248717</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000967956207&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000852369430&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2763,22 +2763,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Noor Shahirah Othman</t>
+          <t>Shameel Isfahan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>26191985463784477</t>
+          <t>25409058178770177</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26191985463784477</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1499602983&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000919091091&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Replied</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>No Reply</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2821,22 +2821,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nor Azlina Abdullah</t>
+          <t>Shazlin Rosly</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>26710435991927086</t>
+          <t>26809398435345201</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26710435991927086</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000906505750&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000837096448&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2879,22 +2879,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Normah Hussin Snowwhite</t>
+          <t>Siti Norfqizqh Kqmqruzqmqn</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>27126157506973707</t>
+          <t>2009668263</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/27126157506973707</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/2009668263</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100007315901018&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001587679680&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2937,22 +2937,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nur Abas</t>
+          <t>Staphyine Cyril</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>34997155886550414</t>
+          <t>409375743</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34997155886550414</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/409375743</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100008708016731&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=563533491&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2995,22 +2995,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Nur Hidayah</t>
+          <t>Syaidatul Farah</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>34244179895228874</t>
+          <t>638705431</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34244179895228874</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/638705431</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100040767291999&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100004598078870&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3053,22 +3053,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nur Kiawati Wahib</t>
+          <t>Syikin Supian</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>26623628940658692</t>
+          <t>26634227206261458</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26623628940658692</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26634227206261458</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100003056737346&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001746488721&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3111,22 +3111,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nur Lisya Nadirah</t>
+          <t>Ummi Kalsum</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>177043204</t>
+          <t>26528731786791901</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/177043204</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/26528731786791901</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100009946593657&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100014669568622&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3169,22 +3169,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nuraina Shahirah</t>
+          <t>Wan Aisyah</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>26102771442752311</t>
+          <t>34168977156079212</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26102771442752311</t>
+          <t>https://app.manychat.com/fb594456394024035/chat/34168977156079212</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100010187793274&amp;thread_type=FB_MESSAGE</t>
+          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100028228477866&amp;thread_type=FB_MESSAGE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3224,1050 +3224,6 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Nurarina Khidir</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>26564918653192753</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26564918653192753</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100002452361904&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Nurnadia Kamaruzzaman</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>26692733340416745</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26692733340416745</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000512649285&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Nurul Knewrul</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>35133283479620209</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/35133283479620209</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001049088069&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Rasidah Rosmanan</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>35023451573969923</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/35023451573969923</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001914029091&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Rijah Weiwei</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>26456046297334143</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26456046297334143</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000960038530&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Salmah Jaafar</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>26750312877989179</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26750312877989179</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000547021795&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Sariffudin Fiza</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>25640455475627828</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25640455475627828</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000852369430&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Shameel Isfahan</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>25409058178770177</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/25409058178770177</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000919091091&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Shazlin Rosly</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>26809398435345201</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26809398435345201</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100000837096448&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Siti Norfqizqh Kqmqruzqmqn</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2009668263</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/2009668263</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001587679680&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Staphyine Cyril</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>409375743</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/409375743</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=563533491&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Suhaida M Sobri</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>26458022533837392</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26458022533837392</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=682577879&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Syaidatul Farah</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>638705431</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/638705431</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100004598078870&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Syikin Supian</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>26634227206261458</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26634227206261458</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100001746488721&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Sylvia Hsuanfu Chen</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>26550612654593061</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26550612654593061</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=759338394&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Ummi Kalsum</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>26528731786791901</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/26528731786791901</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100014669568622&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Wan Aisyah</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>34168977156079212</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/34168977156079212</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=100028228477866&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Yew Ng</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>51023365</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://app.manychat.com/fb594456394024035/chat/51023365</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://business.facebook.com/latest/inbox/all/?asset_id=594456394024035&amp;mailbox_id=594456394024035&amp;selected_item_id=1405004216&amp;thread_type=FB_MESSAGE</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2026-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Replied</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>No Reply</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Incomplete</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
